--- a/System_Interface_Design.xlsx
+++ b/System_Interface_Design.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3A38AC-7E2D-4B3E-99F0-304F00EFB9A7}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7117FD4-01D8-47FF-9BED-E53DDA4B9065}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="100" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="130" yWindow="50" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -295,10 +295,10 @@
     <t>Notification of unidentifiable Receiver</t>
   </si>
   <si>
-    <t>Share Annotated Audio File</t>
-  </si>
-  <si>
     <t>Annotated audio file(s)</t>
+  </si>
+  <si>
+    <t>Share Annotated Audio Files</t>
   </si>
 </sst>
 </file>
@@ -935,7 +935,7 @@
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B33" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>84</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C51" s="13" t="s">
         <v>87</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C53" s="18" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D53" t="s">
         <v>49</v>

--- a/System_Interface_Design.xlsx
+++ b/System_Interface_Design.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thoma\Documents\GitHub\Audio_Analyzer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7117FD4-01D8-47FF-9BED-E53DDA4B9065}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80528D90-29C7-4A50-BDF3-43DE37BD656C}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="130" yWindow="50" windowWidth="19060" windowHeight="20670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="110">
   <si>
     <t>Name</t>
   </si>
@@ -141,12 +141,6 @@
     <t>Non-Data Bytes</t>
   </si>
   <si>
-    <t>Amalgamation</t>
-  </si>
-  <si>
-    <t>An audio signal</t>
-  </si>
-  <si>
     <t>Rests and notes</t>
   </si>
   <si>
@@ -174,9 +168,6 @@
     <t>Signal that each audio file should be uploaded by the system</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>Signal to abandon audio file</t>
   </si>
   <si>
@@ -216,9 +207,6 @@
     <t>Signal to process audio files</t>
   </si>
   <si>
-    <t>Signal to abandon processing audio file</t>
-  </si>
-  <si>
     <t>Set of all unprocessed uploaded audio files for which the Worker has permission to process</t>
   </si>
   <si>
@@ -241,9 +229,6 @@
   </si>
   <si>
     <t>Listen and View</t>
-  </si>
-  <si>
-    <t>Signal of desire to listen / view an amalgamation (see amalgamation in outputs)</t>
   </si>
   <si>
     <t>rest</t>
@@ -274,12 +259,6 @@
     <t>an array of 16-bit integers that represents music or speech</t>
   </si>
   <si>
-    <t>Request to listen to audio and view visualizations in an amalgation</t>
-  </si>
-  <si>
-    <t>Set of all amalgamations for which the Listener / Viewer has permission to listen / view</t>
-  </si>
-  <si>
     <t>Signal of desire to share</t>
   </si>
   <si>
@@ -299,6 +278,86 @@
   </si>
   <si>
     <t>Share Annotated Audio Files</t>
+  </si>
+  <si>
+    <t>Click of a circular red button with a white "X" in the middle.</t>
+  </si>
+  <si>
+    <t>Click of a circular red button with a white "X" In the middle.
+Button is upload specific and only available during upload.</t>
+  </si>
+  <si>
+    <t>Checking check boxes next to audio files available for processing</t>
+  </si>
+  <si>
+    <t>Signal of desire to listen / view an annotated audio file</t>
+  </si>
+  <si>
+    <t>Request to listen to audio and view visualizations in an annotated audio file</t>
+  </si>
+  <si>
+    <t>Click on the name of the annotated audio file</t>
+  </si>
+  <si>
+    <t>Signal to abandon processing audio files</t>
+  </si>
+  <si>
+    <t>Request that the system share annotated audio file(s) with the specified Receiver(s)</t>
+  </si>
+  <si>
+    <t>Typed email addresses delimited by commas or semicolons</t>
+  </si>
+  <si>
+    <t>Click of an enabled "Share" button</t>
+  </si>
+  <si>
+    <t>Click of an enabled "Upload" button</t>
+  </si>
+  <si>
+    <t>Click of an enabled "Process" button</t>
+  </si>
+  <si>
+    <t>Checking check boxes next to audio files available for sharing</t>
+  </si>
+  <si>
+    <t>Browse feature provided initially and after each upload,
+including "Name" field, "Path" field, and "Set" button</t>
+  </si>
+  <si>
+    <t>Set of all annotated audio files for which the Listener / Viewer has permission to listen / view</t>
+  </si>
+  <si>
+    <t>Annotated audio file</t>
+  </si>
+  <si>
+    <t>Audio signal</t>
+  </si>
+  <si>
+    <t>List of names of listen/view-able audio files</t>
+  </si>
+  <si>
+    <t>Table of names of processable audio files and check boxes</t>
+  </si>
+  <si>
+    <t>Table of names of shareable audio files and check boxes</t>
+  </si>
+  <si>
+    <t>Formatting text corresponding to Receiver red</t>
+  </si>
+  <si>
+    <t>Email with links to app to view an annotated audio file</t>
+  </si>
+  <si>
+    <t>Clicking "Upload" in a menu</t>
+  </si>
+  <si>
+    <t>Clicking "Process" in a menu</t>
+  </si>
+  <si>
+    <t>Clicking "Listen and View" in a menu</t>
+  </si>
+  <si>
+    <t>Clicking "Share" in a menu</t>
   </si>
 </sst>
 </file>
@@ -377,7 +436,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -417,7 +476,17 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -706,12 +775,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E76"/>
+  <dimension ref="A2:E77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="28.26953125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="81.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="37.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="54.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="13.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -732,12 +801,12 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="B9" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>0</v>
@@ -747,436 +816,434 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B10" s="20" t="s">
-        <v>59</v>
+      <c r="B10" s="22" t="s">
+        <v>56</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B11" s="20"/>
-      <c r="C11" s="20" t="s">
-        <v>47</v>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22" t="s">
+        <v>45</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B12" s="20"/>
-      <c r="C12" s="20"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
       <c r="D12" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
       <c r="D13" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
       <c r="D14" s="7" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B15" s="20"/>
-      <c r="C15" s="21"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B16" s="20"/>
-      <c r="C16" s="21"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="17" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B17" s="20"/>
-      <c r="C17" s="21"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="23"/>
       <c r="D17" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B18" s="20"/>
-      <c r="C18" s="21"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="23"/>
       <c r="D18" s="7" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B19" s="20"/>
-      <c r="C19" s="21"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="7" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B20" s="20"/>
-      <c r="C20" s="21"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="23"/>
       <c r="D20" s="7" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="20"/>
-      <c r="C21" s="21"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="23"/>
       <c r="D21" s="7" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="23"/>
       <c r="D22" s="8" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B23" s="20"/>
-      <c r="C23" s="21"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B24" s="20"/>
-      <c r="C24" s="21"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B25" s="20"/>
+      <c r="B25" s="22"/>
       <c r="C25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="D25" s="16" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B26" s="22"/>
+      <c r="C26" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="25" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B27" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D27" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B28" s="22"/>
+      <c r="C28" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B29" s="22"/>
+      <c r="C29" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B30" s="22"/>
+      <c r="C30" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="16" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B31" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D31" s="16" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B32" s="22"/>
+      <c r="C32" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B33" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="14" t="s">
+        <v>77</v>
+      </c>
+      <c r="D33" s="16" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B34" s="22"/>
+      <c r="C34" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B35" s="22"/>
+      <c r="C35" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="D35" s="16" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B36" s="20"/>
+      <c r="C36" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B39" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B40" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="D25" s="16" t="s">
+      <c r="D40" s="26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B41" s="24"/>
+      <c r="C41" s="15" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B26" s="20"/>
-      <c r="C26" s="5" t="s">
+      <c r="D41" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B27" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="5" t="s">
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B42" s="24"/>
+      <c r="C42" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B43" s="24"/>
+      <c r="C43" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B44" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C44" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B28" s="20"/>
-      <c r="C28" s="5" t="s">
+      <c r="D44" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B45" s="22"/>
+      <c r="C45" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="D28" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B29" s="20"/>
-      <c r="C29" s="5" t="s">
+      <c r="D45" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B30" s="20"/>
-      <c r="C30" s="5" t="s">
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B46" s="22"/>
+      <c r="C46" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D30" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B31" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B32" s="20"/>
-      <c r="C32" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B33" s="20" t="s">
-        <v>90</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D33" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B34" s="20"/>
-      <c r="C34" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="D34" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B35" s="20"/>
-      <c r="C35" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B38" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B39" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>51</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B40" s="22"/>
-      <c r="C40" s="15" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B41" s="22"/>
-      <c r="C41" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B42" s="22"/>
-      <c r="C42" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B43" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="D46" t="s">
         <v>64</v>
       </c>
-      <c r="D43" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B44" s="20"/>
-      <c r="C44" s="4" t="s">
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B47" s="22"/>
+      <c r="C47" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D47" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B45" s="20"/>
-      <c r="C45" s="4" t="s">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="B48" s="22" t="s">
         <v>67</v>
       </c>
-      <c r="D45" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B46" s="20"/>
-      <c r="C46" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B47" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="4" t="s">
+      <c r="C48" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B49" s="22"/>
+      <c r="C49" s="22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D49" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B50" s="22"/>
+      <c r="C50" s="22"/>
+      <c r="D50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B52" t="s">
         <v>83</v>
       </c>
-      <c r="D47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="B48" s="20"/>
-      <c r="C48" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B49" s="20"/>
-      <c r="C49" s="20"/>
-      <c r="D49" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B50" s="20"/>
-      <c r="C50" s="20"/>
-      <c r="D50" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
-        <v>90</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D51" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="C52" s="18" t="s">
-        <v>88</v>
+      <c r="C52" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="D52" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="C53" s="18" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="C54" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="D54" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A56" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B56" s="3" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B57" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="D56" t="s">
+      <c r="D57" t="s">
         <v>32</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E57" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B57" s="9" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B58" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C57" s="6" t="s">
+      <c r="C58" s="6" t="s">
         <v>23</v>
-      </c>
-      <c r="D57">
-        <v>4</v>
-      </c>
-      <c r="E57">
-        <f>SUM(D57:D70)</f>
-        <v>44</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B58" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>31</v>
       </c>
       <c r="D58">
         <v>4</v>
       </c>
+      <c r="E58">
+        <f>SUM(D58:D71)</f>
+        <v>44</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B59" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D59">
         <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="B60" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="7" t="s">
-        <v>25</v>
+      <c r="B60" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="D60">
         <v>4</v>
@@ -1184,10 +1251,10 @@
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B61" s="11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D61">
         <v>4</v>
@@ -1195,21 +1262,21 @@
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B62" s="11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D62">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B63" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C63" s="7">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>27</v>
       </c>
       <c r="D63">
         <v>2</v>
@@ -1217,137 +1284,148 @@
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="B64" s="11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64" s="7">
-        <v>48000</v>
+        <v>1</v>
       </c>
       <c r="D64">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B65" s="11" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C65" s="7">
-        <v>16</v>
+        <v>48000</v>
       </c>
       <c r="D65">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B66" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C66" s="7">
         <v>16</v>
       </c>
-      <c r="C66" s="7" t="s">
-        <v>29</v>
-      </c>
       <c r="D66">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B67" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D67">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B68" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D67">
+      <c r="D68">
         <v>2</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B68" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D68">
-        <v>4</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B69" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C69" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B70" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C69" s="8" t="s">
+      <c r="C70" s="8" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B70" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="D70">
-        <v>4</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B71" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="C71" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D71">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B72" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C71" s="8" t="s">
+      <c r="C72" s="8" t="s">
         <v>36</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B72" t="s">
-        <v>42</v>
-      </c>
-      <c r="C72" s="16" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>73</v>
+        <v>40</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C74" s="16" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C75" s="16" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>79</v>
-      </c>
-      <c r="C76" s="17" t="s">
-        <v>80</v>
+        <v>72</v>
+      </c>
+      <c r="C76" s="16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" ht="29" x14ac:dyDescent="0.35">
+      <c r="B77" t="s">
+        <v>74</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C48:C50"/>
-    <mergeCell ref="B47:B50"/>
+    <mergeCell ref="C49:C51"/>
+    <mergeCell ref="B48:B51"/>
     <mergeCell ref="B33:B35"/>
-    <mergeCell ref="B43:B46"/>
+    <mergeCell ref="B44:B47"/>
     <mergeCell ref="C11:C24"/>
     <mergeCell ref="B10:B26"/>
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="B31:B32"/>
-    <mergeCell ref="B39:B42"/>
+    <mergeCell ref="B40:B43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
